--- a/artfynd/A 46058-2025 artfynd.xlsx
+++ b/artfynd/A 46058-2025 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111896649</v>
+        <v>111895085</v>
       </c>
       <c r="B2" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -709,19 +704,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kratte masugn, Gstr</t>
+          <t>Kratte masugn, Kratte masugn, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576354</v>
+        <v>576346</v>
       </c>
       <c r="R2" t="n">
         <v>6702382</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,9 +744,19 @@
           <t>2023-09-04</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +771,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>fanny westling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111895085</v>
+        <v>111896649</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -811,20 +812,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kratte masugn (Kratte masugn), Gstr</t>
+          <t>Kratte masugn, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576346</v>
+        <v>576354</v>
       </c>
       <c r="R3" t="n">
-        <v>6702382</v>
+        <v>6702381</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,19 +851,9 @@
           <t>2023-09-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:38</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,12 +868,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>fanny westling</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 46058-2025 artfynd.xlsx
+++ b/artfynd/A 46058-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111895085</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,8 +887,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111896649</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>